--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92818</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91634</v>
+        <v>91636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92452</v>
+        <v>92455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>87547</v>
+        <v>87549</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>87547</v>
+        <v>87549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89314</v>
+        <v>89316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99680</v>
+        <v>99683</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93423</v>
+        <v>93426</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92455</v>
+        <v>92456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99683</v>
+        <v>99684</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93426</v>
+        <v>93427</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92822</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92456</v>
+        <v>92461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>87586</v>
+        <v>87588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>87549</v>
+        <v>87551</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>87549</v>
+        <v>87551</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99684</v>
+        <v>99689</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93427</v>
+        <v>93432</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 34775-2023 artfynd.xlsx
+++ b/artfynd/A 34775-2023 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>136246185</v>
       </c>
       <c r="B7" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136195675</v>
       </c>
       <c r="B8" t="n">
-        <v>91638</v>
+        <v>91640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136195674</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136246184</v>
       </c>
       <c r="B10" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136246189</v>
       </c>
       <c r="B11" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136246183</v>
       </c>
       <c r="B12" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>136246188</v>
       </c>
       <c r="B14" t="n">
-        <v>92461</v>
+        <v>92463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>136202511</v>
       </c>
       <c r="B15" t="n">
-        <v>87588</v>
+        <v>87590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136202482</v>
       </c>
       <c r="B16" t="n">
-        <v>87551</v>
+        <v>87553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136202509</v>
       </c>
       <c r="B17" t="n">
-        <v>87551</v>
+        <v>87553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136202506</v>
       </c>
       <c r="B18" t="n">
-        <v>89318</v>
+        <v>89320</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>136200761</v>
       </c>
       <c r="B20" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>136195691</v>
       </c>
       <c r="B64" t="n">
-        <v>99689</v>
+        <v>99691</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>136196782</v>
       </c>
       <c r="B80" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>136202502</v>
       </c>
       <c r="B87" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
